--- a/artfynd/A 51033-2025 artfynd.xlsx
+++ b/artfynd/A 51033-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,6 +804,213 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129524454</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92834</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>788</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gul taggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum geogenium</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Långkärret, Långkärret, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>545095</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6654286</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Inventerar med Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Matilda Aalto</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Matilda Aalto, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129524481</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92868</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långkärret, Långkärret, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>545100</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6654274</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Matilda Aalto</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Matilda Aalto, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51033-2025 artfynd.xlsx
+++ b/artfynd/A 51033-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>129524454</v>
       </c>
       <c r="B3" t="n">
-        <v>92834</v>
+        <v>92837</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129524481</v>
       </c>
       <c r="B4" t="n">
-        <v>92868</v>
+        <v>92871</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 51033-2025 artfynd.xlsx
+++ b/artfynd/A 51033-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>129524454</v>
       </c>
       <c r="B3" t="n">
-        <v>92837</v>
+        <v>92865</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129524481</v>
       </c>
       <c r="B4" t="n">
-        <v>92871</v>
+        <v>92899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 51033-2025 artfynd.xlsx
+++ b/artfynd/A 51033-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>129524454</v>
       </c>
       <c r="B3" t="n">
-        <v>92865</v>
+        <v>92871</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129524481</v>
       </c>
       <c r="B4" t="n">
-        <v>92899</v>
+        <v>92905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 51033-2025 artfynd.xlsx
+++ b/artfynd/A 51033-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>129524454</v>
       </c>
       <c r="B3" t="n">
-        <v>92871</v>
+        <v>92872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129524481</v>
       </c>
       <c r="B4" t="n">
-        <v>92905</v>
+        <v>92906</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 51033-2025 artfynd.xlsx
+++ b/artfynd/A 51033-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>129524454</v>
       </c>
       <c r="B3" t="n">
-        <v>92872</v>
+        <v>92877</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129524481</v>
       </c>
       <c r="B4" t="n">
-        <v>92906</v>
+        <v>92911</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 51033-2025 artfynd.xlsx
+++ b/artfynd/A 51033-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>129524454</v>
       </c>
       <c r="B3" t="n">
-        <v>92877</v>
+        <v>92881</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129524481</v>
       </c>
       <c r="B4" t="n">
-        <v>92911</v>
+        <v>92915</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 51033-2025 artfynd.xlsx
+++ b/artfynd/A 51033-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>129524454</v>
       </c>
       <c r="B3" t="n">
-        <v>92881</v>
+        <v>92883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129524481</v>
       </c>
       <c r="B4" t="n">
-        <v>92915</v>
+        <v>92917</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 51033-2025 artfynd.xlsx
+++ b/artfynd/A 51033-2025 artfynd.xlsx
@@ -675,68 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16097950</v>
+        <v>129524454</v>
       </c>
       <c r="B2" t="n">
-        <v>96232</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219795</v>
+        <v>788</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>knoppbristning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>ötjärnsvägen, Vstm</t>
+          <t>Långkärret, Långkärret, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545283.2170594534</v>
+        <v>545095</v>
       </c>
       <c r="R2" t="n">
-        <v>6654348.562299074</v>
+        <v>6654286</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,27 +743,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-07-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-07-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Den lever farligt. skogsvägkanten där den växer slås av och till. Den här växte någon meter från vägkanten lite nedom vägytan</t>
+          <t>Inventerar med Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,28 +762,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sten Mu Yu Widhe</t>
+          <t>Matilda Aalto</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sten Mu Yu Widhe, Birgitta Widhe</t>
+          <t>Matilda Aalto, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129524454</v>
+        <v>129524481</v>
       </c>
       <c r="B3" t="n">
-        <v>92883</v>
+        <v>93233</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>788</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -845,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545095</v>
+        <v>545100</v>
       </c>
       <c r="R3" t="n">
-        <v>6654286</v>
+        <v>6654274</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,11 +855,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Inventerar med Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129524481</v>
+        <v>2636958</v>
       </c>
       <c r="B4" t="n">
-        <v>92917</v>
+        <v>99017</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,40 +893,52 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>219795</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långkärret, Långkärret, Vstm</t>
+          <t>ötjärnsvägen, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545100</v>
+        <v>545283</v>
       </c>
       <c r="R4" t="n">
-        <v>6654274</v>
+        <v>6654349</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,12 +962,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2012-08-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2012-08-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,19 +976,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>vägkant</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>näringsfattig jord</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Matilda Aalto</t>
+          <t>Sten Mu Yu Widhe</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Matilda Aalto, Sebastian Kirppu</t>
+          <t>Sten Mu Yu Widhe, Birgitta Widhe</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 51033-2025 artfynd.xlsx
+++ b/artfynd/A 51033-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524454</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524481</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,8 +1016,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2636958</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>